--- a/data/raw/sales/Week 13/Nexlev/other_channels.xlsx
+++ b/data/raw/sales/Week 13/Nexlev/other_channels.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>ET-02 Green</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="D2" s="13" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>ETC-04 White</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="D5" s="13" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>ETC-05</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="D7" s="34" t="n">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>GS-5</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="D7" s="16" t="n">
@@ -2770,7 +2770,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>ETC-07</t>
+          <t>ETC-07-WH</t>
         </is>
       </c>
       <c r="D38" s="16" t="n">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>ETC-08-BL</t>
         </is>
       </c>
       <c r="D40" s="16" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>V-01-RG</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="D44" s="16" t="n">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="D54" s="24" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E54" s="17" t="n">
@@ -6781,7 +6781,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>FBA79598</t>
+          <t>FBK79598</t>
         </is>
       </c>
       <c r="B3" s="16" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>ETC-08-BL</t>
         </is>
       </c>
       <c r="D6" s="27" t="n">
@@ -6973,7 +6973,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="29" t="inlineStr">
         <is>
-          <t>FBA79374</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B2" s="16" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="C2" s="29" t="inlineStr">
         <is>
-          <t>ET-02</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="D2" s="27" t="n">
@@ -7204,7 +7204,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>CM-02</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
@@ -7336,7 +7336,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>FBA79707</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
@@ -7666,7 +7666,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="27" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
